--- a/INDiGO Trial/Call List/IP Accountability Log/SupplementationReport_October Ends.xlsx
+++ b/INDiGO Trial/Call List/IP Accountability Log/SupplementationReport_October Ends.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lshtm-my.sharepoint.com/personal/lshyc1_lshtm_ac_uk/Documents/Desktop/INDiGO Trial/Call List/IP Accountability Log/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{7171C9C8-5535-4F30-ABE3-1FF1BABFC289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAAED7B5-2D8B-4B86-84A5-66D8E5630D42}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{7171C9C8-5535-4F30-ABE3-1FF1BABFC289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DCADA28-EEE5-4ED5-9605-C873FB49245F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3AE563DE-395F-4274-A118-74C8C6972D57}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{3AE563DE-395F-4274-A118-74C8C6972D57}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,122 +36,29 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
   <si>
     <t>P</t>
   </si>
   <si>
-    <t>Jattaba</t>
-  </si>
-  <si>
-    <t>Fatou Sanneh</t>
-  </si>
-  <si>
-    <t>04-026-059L</t>
-  </si>
-  <si>
-    <t>IN-C-181C</t>
-  </si>
-  <si>
-    <t>IN-M-181B</t>
-  </si>
-  <si>
     <t>T</t>
   </si>
   <si>
-    <t>Halimatou Tabally</t>
-  </si>
-  <si>
-    <t>41-032-02</t>
-  </si>
-  <si>
-    <t>IN-C-160B</t>
-  </si>
-  <si>
-    <t>IN-M-160G</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
-    <t>Jiffarong</t>
-  </si>
-  <si>
-    <t>Safiatou Touray</t>
-  </si>
-  <si>
-    <t>06-006-018S</t>
-  </si>
-  <si>
-    <t>IN-C-150K</t>
-  </si>
-  <si>
-    <t>IN-M-150H</t>
-  </si>
-  <si>
-    <t>Bajana</t>
-  </si>
-  <si>
-    <t>Aja Drammeh</t>
-  </si>
-  <si>
-    <t>06-015-006K</t>
-  </si>
-  <si>
-    <t>IN-C-148K</t>
-  </si>
-  <si>
-    <t>IN-M-148E</t>
-  </si>
-  <si>
     <t>W</t>
   </si>
   <si>
-    <t>Jankey Mariama Samateh</t>
-  </si>
-  <si>
-    <t>11-028-033D</t>
-  </si>
-  <si>
-    <t>IN-C-146G</t>
-  </si>
-  <si>
-    <t>IN-M-146H</t>
-  </si>
-  <si>
     <t>E</t>
   </si>
   <si>
     <t>Keneba</t>
   </si>
   <si>
-    <t>Masireh Sise</t>
-  </si>
-  <si>
-    <t>29-005-207X</t>
-  </si>
-  <si>
-    <t>IN-C-134F</t>
-  </si>
-  <si>
-    <t>IN-M-134C</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
-    <t>Bintou Sise</t>
-  </si>
-  <si>
-    <t>10-011-031R</t>
-  </si>
-  <si>
-    <t>IN-C-132B</t>
-  </si>
-  <si>
-    <t>IN-M-132C</t>
-  </si>
-  <si>
     <t>Infant DoB</t>
   </si>
   <si>
@@ -183,13 +90,148 @@
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>IN-M-162F</t>
+  </si>
+  <si>
+    <t>IN-M-180J</t>
+  </si>
+  <si>
+    <t>IN-M-192B</t>
+  </si>
+  <si>
+    <t>IN-M-194D</t>
+  </si>
+  <si>
+    <t>IN-M-195J</t>
+  </si>
+  <si>
+    <t>IN-M-207C</t>
+  </si>
+  <si>
+    <t>IN-M-214F</t>
+  </si>
+  <si>
+    <t>IN-M-221E</t>
+  </si>
+  <si>
+    <t>IN-M-224K</t>
+  </si>
+  <si>
+    <t>IN-M-232C</t>
+  </si>
+  <si>
+    <t>IN-C-162P</t>
+  </si>
+  <si>
+    <t>IN-C-180E</t>
+  </si>
+  <si>
+    <t>IN-C-192G</t>
+  </si>
+  <si>
+    <t>IN-C-194H</t>
+  </si>
+  <si>
+    <t>IN-C-195C</t>
+  </si>
+  <si>
+    <t>IN-C-207A</t>
+  </si>
+  <si>
+    <t>IN-C-214G</t>
+  </si>
+  <si>
+    <t>IN-C-221F</t>
+  </si>
+  <si>
+    <t>IN-C-224E</t>
+  </si>
+  <si>
+    <t>IN-C-232A</t>
+  </si>
+  <si>
+    <t>03-052-021L</t>
+  </si>
+  <si>
+    <t>41-005-01</t>
+  </si>
+  <si>
+    <t>40-025-13</t>
+  </si>
+  <si>
+    <t>02-015-012M</t>
+  </si>
+  <si>
+    <t>29-056-047H</t>
+  </si>
+  <si>
+    <t>76-027-01</t>
+  </si>
+  <si>
+    <t>76-009-01</t>
+  </si>
+  <si>
+    <t>47-041-06</t>
+  </si>
+  <si>
+    <t>03-061-006A</t>
+  </si>
+  <si>
+    <t>41-021-01</t>
+  </si>
+  <si>
+    <t>Mariama Jobe</t>
+  </si>
+  <si>
+    <t>Nioro Jattaba</t>
+  </si>
+  <si>
+    <t>Fanta Mama Sawaneh</t>
+  </si>
+  <si>
+    <t>KWINELLA SANSANKONO</t>
+  </si>
+  <si>
+    <t>Jalika Nduru</t>
+  </si>
+  <si>
+    <t>WUROKANG</t>
+  </si>
+  <si>
+    <t>Sajou Drammeh</t>
+  </si>
+  <si>
+    <t>Sankandi</t>
+  </si>
+  <si>
+    <t>Sainabou Sambou</t>
+  </si>
+  <si>
+    <t>Joko Jawara</t>
+  </si>
+  <si>
+    <t>Mai Beyai</t>
+  </si>
+  <si>
+    <t>Hawa Sorra</t>
+  </si>
+  <si>
+    <t>NEMA</t>
+  </si>
+  <si>
+    <t>Mariama Sowe</t>
+  </si>
+  <si>
+    <t>Jainaba Jarju</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -207,6 +249,14 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -233,15 +283,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -249,6 +300,7 @@
   <dxfs count="11">
     <dxf>
       <font>
+        <b/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -394,7 +446,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -421,8 +472,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AC6DCDAC-AB53-4B81-9B07-5120EBDFE7DE}" name="Table2" displayName="Table2" ref="A2:I9" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
-  <autoFilter ref="A2:I9" xr:uid="{AC6DCDAC-AB53-4B81-9B07-5120EBDFE7DE}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AC6DCDAC-AB53-4B81-9B07-5120EBDFE7DE}" name="Table2" displayName="Table2" ref="A2:I12" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A2:I12" xr:uid="{AC6DCDAC-AB53-4B81-9B07-5120EBDFE7DE}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -434,8 +485,8 @@
     <filterColumn colId="8" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{8A2F8392-C67F-470A-BC25-D5D0917EA908}" name="ID" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{75C4A6A5-235D-42C5-A3D3-1A43202F80C5}" name="INFANT ID" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{8A2F8392-C67F-470A-BC25-D5D0917EA908}" name="ID" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{75C4A6A5-235D-42C5-A3D3-1A43202F80C5}" name="INFANT ID" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{8985A38F-5108-4AA4-A3B9-02CE8BA69515}" name="KIANG No." dataDxfId="8"/>
     <tableColumn id="4" xr3:uid="{03E4A584-CF86-430E-BDB4-246F9195A662}" name="NAME" dataDxfId="7"/>
     <tableColumn id="5" xr3:uid="{1B475176-EE49-4A17-BE21-2B6A2F7A1269}" name="VILLAGE" dataDxfId="6"/>
@@ -765,265 +816,324 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{979AF763-B92E-442F-AC72-5562B3A357D4}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="A1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>45</v>
+      <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="A3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="4">
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="3">
         <v>45257</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="4">
+      <c r="G3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="3">
         <v>45397</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="4">
         <v>45579</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="A4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="3">
         <v>45243</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="4">
+      <c r="G4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="3">
         <v>45391</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="4">
         <v>45573</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4">
+      <c r="A5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="3">
         <v>45250</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="G5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="3">
         <v>45403</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="4">
         <v>45585</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="3">
         <v>45279</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="4">
+      <c r="G6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" s="3">
         <v>45410</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="4">
         <v>45592</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="A7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="3">
         <v>45243</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="G7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H7" s="3">
         <v>45389</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="4">
         <v>45571</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="4">
+      <c r="A8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8"/>
+      <c r="F8" s="3">
         <v>45236</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" s="4">
+      <c r="G8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
         <v>45390</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="4">
         <v>45572</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="A9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9"/>
+      <c r="F9" s="3">
         <v>45267</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="3">
         <v>45405</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="4">
         <v>45587</v>
       </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
